--- a/output/graficos_nacionales/plot_nacional_e_rezjov_a_2021.xlsx
+++ b/output/graficos_nacionales/plot_nacional_e_rezjov_a_2021.xlsx
@@ -15221,7 +15221,7 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>Rezago respecto a la población de 6 a 21 años</t>
+          <t>Por comunas</t>
         </is>
       </c>
     </row>

--- a/output/graficos_nacionales/plot_nacional_e_rezjov_a_2021.xlsx
+++ b/output/graficos_nacionales/plot_nacional_e_rezjov_a_2021.xlsx
@@ -416,7 +416,7 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>Aysén</t>
+          <t>Aysen</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
@@ -462,7 +462,7 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>Aysén</t>
+          <t>Aysen</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
@@ -508,7 +508,7 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Aysén</t>
+          <t>Aysen</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
@@ -554,7 +554,7 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Aysén</t>
+          <t>Aysen</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
@@ -600,7 +600,7 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Aysén</t>
+          <t>Aysen</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
@@ -646,7 +646,7 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Aysén</t>
+          <t>Aysen</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
@@ -692,7 +692,7 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Aysén</t>
+          <t>Aysen</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
@@ -738,7 +738,7 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Aysén</t>
+          <t>Aysen</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
@@ -830,7 +830,7 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Aysén</t>
+          <t>Aysen</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
@@ -1244,7 +1244,7 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Valparaíso</t>
+          <t>Valparaiso</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
@@ -1290,7 +1290,7 @@
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Valparaíso</t>
+          <t>Valparaiso</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
@@ -1336,7 +1336,7 @@
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Valparaíso</t>
+          <t>Valparaiso</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
@@ -1704,7 +1704,7 @@
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>Valparaíso</t>
+          <t>Valparaiso</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
@@ -1750,7 +1750,7 @@
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>Valparaíso</t>
+          <t>Valparaiso</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
@@ -1796,7 +1796,7 @@
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>Valparaíso</t>
+          <t>Valparaiso</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
@@ -1934,7 +1934,7 @@
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>Valparaíso</t>
+          <t>Valparaiso</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
@@ -1980,7 +1980,7 @@
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>Valparaíso</t>
+          <t>Valparaiso</t>
         </is>
       </c>
       <c r="D36" t="inlineStr">
@@ -2072,7 +2072,7 @@
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>Valparaíso</t>
+          <t>Valparaiso</t>
         </is>
       </c>
       <c r="D38" t="inlineStr">
@@ -2302,7 +2302,7 @@
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>Valparaíso</t>
+          <t>Valparaiso</t>
         </is>
       </c>
       <c r="D43" t="inlineStr">
@@ -2348,7 +2348,7 @@
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>Valparaíso</t>
+          <t>Valparaiso</t>
         </is>
       </c>
       <c r="D44" t="inlineStr">
@@ -2394,7 +2394,7 @@
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>Valparaíso</t>
+          <t>Valparaiso</t>
         </is>
       </c>
       <c r="D45" t="inlineStr">
@@ -2716,7 +2716,7 @@
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>Valparaíso</t>
+          <t>Valparaiso</t>
         </is>
       </c>
       <c r="D52" t="inlineStr">
@@ -2808,7 +2808,7 @@
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>Valparaíso</t>
+          <t>Valparaiso</t>
         </is>
       </c>
       <c r="D54" t="inlineStr">
@@ -3038,7 +3038,7 @@
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>Ñuble</t>
+          <t>Nuble</t>
         </is>
       </c>
       <c r="D59" t="inlineStr">
@@ -3268,7 +3268,7 @@
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>Valparaíso</t>
+          <t>Valparaiso</t>
         </is>
       </c>
       <c r="D64" t="inlineStr">
@@ -3452,7 +3452,7 @@
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>Ñuble</t>
+          <t>Nuble</t>
         </is>
       </c>
       <c r="D68" t="inlineStr">
@@ -3544,7 +3544,7 @@
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>Valparaíso</t>
+          <t>Valparaiso</t>
         </is>
       </c>
       <c r="D70" t="inlineStr">
@@ -3636,7 +3636,7 @@
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>Valparaíso</t>
+          <t>Valparaiso</t>
         </is>
       </c>
       <c r="D72" t="inlineStr">
@@ -3682,7 +3682,7 @@
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t>Valparaíso</t>
+          <t>Valparaiso</t>
         </is>
       </c>
       <c r="D73" t="inlineStr">
@@ -3866,7 +3866,7 @@
       </c>
       <c r="C77" t="inlineStr">
         <is>
-          <t>Valparaíso</t>
+          <t>Valparaiso</t>
         </is>
       </c>
       <c r="D77" t="inlineStr">
@@ -3912,7 +3912,7 @@
       </c>
       <c r="C78" t="inlineStr">
         <is>
-          <t>Ñuble</t>
+          <t>Nuble</t>
         </is>
       </c>
       <c r="D78" t="inlineStr">
@@ -4096,7 +4096,7 @@
       </c>
       <c r="C82" t="inlineStr">
         <is>
-          <t>Valparaíso</t>
+          <t>Valparaiso</t>
         </is>
       </c>
       <c r="D82" t="inlineStr">
@@ -4142,7 +4142,7 @@
       </c>
       <c r="C83" t="inlineStr">
         <is>
-          <t>Valparaíso</t>
+          <t>Valparaiso</t>
         </is>
       </c>
       <c r="D83" t="inlineStr">
@@ -4188,7 +4188,7 @@
       </c>
       <c r="C84" t="inlineStr">
         <is>
-          <t>Ñuble</t>
+          <t>Nuble</t>
         </is>
       </c>
       <c r="D84" t="inlineStr">
@@ -4234,7 +4234,7 @@
       </c>
       <c r="C85" t="inlineStr">
         <is>
-          <t>Ñuble</t>
+          <t>Nuble</t>
         </is>
       </c>
       <c r="D85" t="inlineStr">
@@ -4556,7 +4556,7 @@
       </c>
       <c r="C92" t="inlineStr">
         <is>
-          <t>Valparaíso</t>
+          <t>Valparaiso</t>
         </is>
       </c>
       <c r="D92" t="inlineStr">
@@ -4602,7 +4602,7 @@
       </c>
       <c r="C93" t="inlineStr">
         <is>
-          <t>Valparaíso</t>
+          <t>Valparaiso</t>
         </is>
       </c>
       <c r="D93" t="inlineStr">
@@ -4786,7 +4786,7 @@
       </c>
       <c r="C97" t="inlineStr">
         <is>
-          <t>Ñuble</t>
+          <t>Nuble</t>
         </is>
       </c>
       <c r="D97" t="inlineStr">
@@ -4970,7 +4970,7 @@
       </c>
       <c r="C101" t="inlineStr">
         <is>
-          <t>Ñuble</t>
+          <t>Nuble</t>
         </is>
       </c>
       <c r="D101" t="inlineStr">
@@ -5016,7 +5016,7 @@
       </c>
       <c r="C102" t="inlineStr">
         <is>
-          <t>Ñuble</t>
+          <t>Nuble</t>
         </is>
       </c>
       <c r="D102" t="inlineStr">
@@ -5246,7 +5246,7 @@
       </c>
       <c r="C107" t="inlineStr">
         <is>
-          <t>Valparaíso</t>
+          <t>Valparaiso</t>
         </is>
       </c>
       <c r="D107" t="inlineStr">
@@ -5338,7 +5338,7 @@
       </c>
       <c r="C109" t="inlineStr">
         <is>
-          <t>Ñuble</t>
+          <t>Nuble</t>
         </is>
       </c>
       <c r="D109" t="inlineStr">
@@ -5430,7 +5430,7 @@
       </c>
       <c r="C111" t="inlineStr">
         <is>
-          <t>Valparaíso</t>
+          <t>Valparaiso</t>
         </is>
       </c>
       <c r="D111" t="inlineStr">
@@ -5522,7 +5522,7 @@
       </c>
       <c r="C113" t="inlineStr">
         <is>
-          <t>Ñuble</t>
+          <t>Nuble</t>
         </is>
       </c>
       <c r="D113" t="inlineStr">
@@ -5614,7 +5614,7 @@
       </c>
       <c r="C115" t="inlineStr">
         <is>
-          <t>Valparaíso</t>
+          <t>Valparaiso</t>
         </is>
       </c>
       <c r="D115" t="inlineStr">
@@ -5706,7 +5706,7 @@
       </c>
       <c r="C117" t="inlineStr">
         <is>
-          <t>Valparaíso</t>
+          <t>Valparaiso</t>
         </is>
       </c>
       <c r="D117" t="inlineStr">
@@ -6074,7 +6074,7 @@
       </c>
       <c r="C125" t="inlineStr">
         <is>
-          <t>Ñuble</t>
+          <t>Nuble</t>
         </is>
       </c>
       <c r="D125" t="inlineStr">
@@ -6304,7 +6304,7 @@
       </c>
       <c r="C130" t="inlineStr">
         <is>
-          <t>Ñuble</t>
+          <t>Nuble</t>
         </is>
       </c>
       <c r="D130" t="inlineStr">
@@ -6350,7 +6350,7 @@
       </c>
       <c r="C131" t="inlineStr">
         <is>
-          <t>Valparaíso</t>
+          <t>Valparaiso</t>
         </is>
       </c>
       <c r="D131" t="inlineStr">
@@ -6442,7 +6442,7 @@
       </c>
       <c r="C133" t="inlineStr">
         <is>
-          <t>Valparaíso</t>
+          <t>Valparaiso</t>
         </is>
       </c>
       <c r="D133" t="inlineStr">
@@ -6764,7 +6764,7 @@
       </c>
       <c r="C140" t="inlineStr">
         <is>
-          <t>Valparaíso</t>
+          <t>Valparaiso</t>
         </is>
       </c>
       <c r="D140" t="inlineStr">
@@ -6810,7 +6810,7 @@
       </c>
       <c r="C141" t="inlineStr">
         <is>
-          <t>Valparaíso</t>
+          <t>Valparaiso</t>
         </is>
       </c>
       <c r="D141" t="inlineStr">
@@ -6856,7 +6856,7 @@
       </c>
       <c r="C142" t="inlineStr">
         <is>
-          <t>Valparaíso</t>
+          <t>Valparaiso</t>
         </is>
       </c>
       <c r="D142" t="inlineStr">
@@ -6902,7 +6902,7 @@
       </c>
       <c r="C143" t="inlineStr">
         <is>
-          <t>Ñuble</t>
+          <t>Nuble</t>
         </is>
       </c>
       <c r="D143" t="inlineStr">
@@ -6948,7 +6948,7 @@
       </c>
       <c r="C144" t="inlineStr">
         <is>
-          <t>Ñuble</t>
+          <t>Nuble</t>
         </is>
       </c>
       <c r="D144" t="inlineStr">
@@ -7454,7 +7454,7 @@
       </c>
       <c r="C155" t="inlineStr">
         <is>
-          <t>Valparaíso</t>
+          <t>Valparaiso</t>
         </is>
       </c>
       <c r="D155" t="inlineStr">
@@ -7822,7 +7822,7 @@
       </c>
       <c r="C163" t="inlineStr">
         <is>
-          <t>Ñuble</t>
+          <t>Nuble</t>
         </is>
       </c>
       <c r="D163" t="inlineStr">
@@ -7960,7 +7960,7 @@
       </c>
       <c r="C166" t="inlineStr">
         <is>
-          <t>Ñuble</t>
+          <t>Nuble</t>
         </is>
       </c>
       <c r="D166" t="inlineStr">
@@ -8282,7 +8282,7 @@
       </c>
       <c r="C173" t="inlineStr">
         <is>
-          <t>Valparaíso</t>
+          <t>Valparaiso</t>
         </is>
       </c>
       <c r="D173" t="inlineStr">
@@ -8466,7 +8466,7 @@
       </c>
       <c r="C177" t="inlineStr">
         <is>
-          <t>Ñuble</t>
+          <t>Nuble</t>
         </is>
       </c>
       <c r="D177" t="inlineStr">
@@ -8558,7 +8558,7 @@
       </c>
       <c r="C179" t="inlineStr">
         <is>
-          <t>Ñuble</t>
+          <t>Nuble</t>
         </is>
       </c>
       <c r="D179" t="inlineStr">
@@ -8604,7 +8604,7 @@
       </c>
       <c r="C180" t="inlineStr">
         <is>
-          <t>Ñuble</t>
+          <t>Nuble</t>
         </is>
       </c>
       <c r="D180" t="inlineStr">
@@ -8788,7 +8788,7 @@
       </c>
       <c r="C184" t="inlineStr">
         <is>
-          <t>Tarapacá</t>
+          <t>Tarapaca</t>
         </is>
       </c>
       <c r="D184" t="inlineStr">
@@ -8834,7 +8834,7 @@
       </c>
       <c r="C185" t="inlineStr">
         <is>
-          <t>Tarapacá</t>
+          <t>Tarapaca</t>
         </is>
       </c>
       <c r="D185" t="inlineStr">
@@ -9248,7 +9248,7 @@
       </c>
       <c r="C194" t="inlineStr">
         <is>
-          <t>Tarapacá</t>
+          <t>Tarapaca</t>
         </is>
       </c>
       <c r="D194" t="inlineStr">
@@ -9294,7 +9294,7 @@
       </c>
       <c r="C195" t="inlineStr">
         <is>
-          <t>Tarapacá</t>
+          <t>Tarapaca</t>
         </is>
       </c>
       <c r="D195" t="inlineStr">
@@ -9432,7 +9432,7 @@
       </c>
       <c r="C198" t="inlineStr">
         <is>
-          <t>Tarapacá</t>
+          <t>Tarapaca</t>
         </is>
       </c>
       <c r="D198" t="inlineStr">
@@ -9846,7 +9846,7 @@
       </c>
       <c r="C207" t="inlineStr">
         <is>
-          <t>Tarapacá</t>
+          <t>Tarapaca</t>
         </is>
       </c>
       <c r="D207" t="inlineStr">
@@ -10582,7 +10582,7 @@
       </c>
       <c r="C223" t="inlineStr">
         <is>
-          <t>Tarapacá</t>
+          <t>Tarapaca</t>
         </is>
       </c>
       <c r="D223" t="inlineStr">
@@ -10628,7 +10628,7 @@
       </c>
       <c r="C224" t="inlineStr">
         <is>
-          <t>Biobío</t>
+          <t>Biobio</t>
         </is>
       </c>
       <c r="D224" t="inlineStr">
@@ -10720,7 +10720,7 @@
       </c>
       <c r="C226" t="inlineStr">
         <is>
-          <t>La Araucanía</t>
+          <t>La Araucania</t>
         </is>
       </c>
       <c r="D226" t="inlineStr">
@@ -10858,7 +10858,7 @@
       </c>
       <c r="C229" t="inlineStr">
         <is>
-          <t>La Araucanía</t>
+          <t>La Araucania</t>
         </is>
       </c>
       <c r="D229" t="inlineStr">
@@ -10904,7 +10904,7 @@
       </c>
       <c r="C230" t="inlineStr">
         <is>
-          <t>Biobío</t>
+          <t>Biobio</t>
         </is>
       </c>
       <c r="D230" t="inlineStr">
@@ -11042,7 +11042,7 @@
       </c>
       <c r="C233" t="inlineStr">
         <is>
-          <t>Los Ríos</t>
+          <t>Los Rios</t>
         </is>
       </c>
       <c r="D233" t="inlineStr">
@@ -11318,7 +11318,7 @@
       </c>
       <c r="C239" t="inlineStr">
         <is>
-          <t>La Araucanía</t>
+          <t>La Araucania</t>
         </is>
       </c>
       <c r="D239" t="inlineStr">
@@ -11410,7 +11410,7 @@
       </c>
       <c r="C241" t="inlineStr">
         <is>
-          <t>Biobío</t>
+          <t>Biobio</t>
         </is>
       </c>
       <c r="D241" t="inlineStr">
@@ -11456,7 +11456,7 @@
       </c>
       <c r="C242" t="inlineStr">
         <is>
-          <t>Biobío</t>
+          <t>Biobio</t>
         </is>
       </c>
       <c r="D242" t="inlineStr">
@@ -11502,7 +11502,7 @@
       </c>
       <c r="C243" t="inlineStr">
         <is>
-          <t>Los Ríos</t>
+          <t>Los Rios</t>
         </is>
       </c>
       <c r="D243" t="inlineStr">
@@ -11548,7 +11548,7 @@
       </c>
       <c r="C244" t="inlineStr">
         <is>
-          <t>La Araucanía</t>
+          <t>La Araucania</t>
         </is>
       </c>
       <c r="D244" t="inlineStr">
@@ -11640,7 +11640,7 @@
       </c>
       <c r="C246" t="inlineStr">
         <is>
-          <t>La Araucanía</t>
+          <t>La Araucania</t>
         </is>
       </c>
       <c r="D246" t="inlineStr">
@@ -11686,7 +11686,7 @@
       </c>
       <c r="C247" t="inlineStr">
         <is>
-          <t>Biobío</t>
+          <t>Biobio</t>
         </is>
       </c>
       <c r="D247" t="inlineStr">
@@ -11778,7 +11778,7 @@
       </c>
       <c r="C249" t="inlineStr">
         <is>
-          <t>Los Ríos</t>
+          <t>Los Rios</t>
         </is>
       </c>
       <c r="D249" t="inlineStr">
@@ -11916,7 +11916,7 @@
       </c>
       <c r="C252" t="inlineStr">
         <is>
-          <t>La Araucanía</t>
+          <t>La Araucania</t>
         </is>
       </c>
       <c r="D252" t="inlineStr">
@@ -11962,7 +11962,7 @@
       </c>
       <c r="C253" t="inlineStr">
         <is>
-          <t>Biobío</t>
+          <t>Biobio</t>
         </is>
       </c>
       <c r="D253" t="inlineStr">
@@ -12054,7 +12054,7 @@
       </c>
       <c r="C255" t="inlineStr">
         <is>
-          <t>La Araucanía</t>
+          <t>La Araucania</t>
         </is>
       </c>
       <c r="D255" t="inlineStr">
@@ -12100,7 +12100,7 @@
       </c>
       <c r="C256" t="inlineStr">
         <is>
-          <t>La Araucanía</t>
+          <t>La Araucania</t>
         </is>
       </c>
       <c r="D256" t="inlineStr">
@@ -12192,7 +12192,7 @@
       </c>
       <c r="C258" t="inlineStr">
         <is>
-          <t>La Araucanía</t>
+          <t>La Araucania</t>
         </is>
       </c>
       <c r="D258" t="inlineStr">
@@ -12238,7 +12238,7 @@
       </c>
       <c r="C259" t="inlineStr">
         <is>
-          <t>Biobío</t>
+          <t>Biobio</t>
         </is>
       </c>
       <c r="D259" t="inlineStr">
@@ -12284,7 +12284,7 @@
       </c>
       <c r="C260" t="inlineStr">
         <is>
-          <t>La Araucanía</t>
+          <t>La Araucania</t>
         </is>
       </c>
       <c r="D260" t="inlineStr">
@@ -12376,7 +12376,7 @@
       </c>
       <c r="C262" t="inlineStr">
         <is>
-          <t>Biobío</t>
+          <t>Biobio</t>
         </is>
       </c>
       <c r="D262" t="inlineStr">
@@ -12422,7 +12422,7 @@
       </c>
       <c r="C263" t="inlineStr">
         <is>
-          <t>La Araucanía</t>
+          <t>La Araucania</t>
         </is>
       </c>
       <c r="D263" t="inlineStr">
@@ -12468,7 +12468,7 @@
       </c>
       <c r="C264" t="inlineStr">
         <is>
-          <t>La Araucanía</t>
+          <t>La Araucania</t>
         </is>
       </c>
       <c r="D264" t="inlineStr">
@@ -12560,7 +12560,7 @@
       </c>
       <c r="C266" t="inlineStr">
         <is>
-          <t>Biobío</t>
+          <t>Biobio</t>
         </is>
       </c>
       <c r="D266" t="inlineStr">
@@ -12606,7 +12606,7 @@
       </c>
       <c r="C267" t="inlineStr">
         <is>
-          <t>La Araucanía</t>
+          <t>La Araucania</t>
         </is>
       </c>
       <c r="D267" t="inlineStr">
@@ -12652,7 +12652,7 @@
       </c>
       <c r="C268" t="inlineStr">
         <is>
-          <t>Biobío</t>
+          <t>Biobio</t>
         </is>
       </c>
       <c r="D268" t="inlineStr">
@@ -12698,7 +12698,7 @@
       </c>
       <c r="C269" t="inlineStr">
         <is>
-          <t>La Araucanía</t>
+          <t>La Araucania</t>
         </is>
       </c>
       <c r="D269" t="inlineStr">
@@ -12790,7 +12790,7 @@
       </c>
       <c r="C271" t="inlineStr">
         <is>
-          <t>Biobío</t>
+          <t>Biobio</t>
         </is>
       </c>
       <c r="D271" t="inlineStr">
@@ -12836,7 +12836,7 @@
       </c>
       <c r="C272" t="inlineStr">
         <is>
-          <t>La Araucanía</t>
+          <t>La Araucania</t>
         </is>
       </c>
       <c r="D272" t="inlineStr">
@@ -12928,7 +12928,7 @@
       </c>
       <c r="C274" t="inlineStr">
         <is>
-          <t>Los Ríos</t>
+          <t>Los Rios</t>
         </is>
       </c>
       <c r="D274" t="inlineStr">
@@ -12974,7 +12974,7 @@
       </c>
       <c r="C275" t="inlineStr">
         <is>
-          <t>Los Ríos</t>
+          <t>Los Rios</t>
         </is>
       </c>
       <c r="D275" t="inlineStr">
@@ -13020,7 +13020,7 @@
       </c>
       <c r="C276" t="inlineStr">
         <is>
-          <t>La Araucanía</t>
+          <t>La Araucania</t>
         </is>
       </c>
       <c r="D276" t="inlineStr">
@@ -13066,7 +13066,7 @@
       </c>
       <c r="C277" t="inlineStr">
         <is>
-          <t>Biobío</t>
+          <t>Biobio</t>
         </is>
       </c>
       <c r="D277" t="inlineStr">
@@ -13112,7 +13112,7 @@
       </c>
       <c r="C278" t="inlineStr">
         <is>
-          <t>Biobío</t>
+          <t>Biobio</t>
         </is>
       </c>
       <c r="D278" t="inlineStr">
@@ -13158,7 +13158,7 @@
       </c>
       <c r="C279" t="inlineStr">
         <is>
-          <t>La Araucanía</t>
+          <t>La Araucania</t>
         </is>
       </c>
       <c r="D279" t="inlineStr">
@@ -13204,7 +13204,7 @@
       </c>
       <c r="C280" t="inlineStr">
         <is>
-          <t>La Araucanía</t>
+          <t>La Araucania</t>
         </is>
       </c>
       <c r="D280" t="inlineStr">
@@ -13250,7 +13250,7 @@
       </c>
       <c r="C281" t="inlineStr">
         <is>
-          <t>La Araucanía</t>
+          <t>La Araucania</t>
         </is>
       </c>
       <c r="D281" t="inlineStr">
@@ -13296,7 +13296,7 @@
       </c>
       <c r="C282" t="inlineStr">
         <is>
-          <t>Biobío</t>
+          <t>Biobio</t>
         </is>
       </c>
       <c r="D282" t="inlineStr">
@@ -13342,7 +13342,7 @@
       </c>
       <c r="C283" t="inlineStr">
         <is>
-          <t>La Araucanía</t>
+          <t>La Araucania</t>
         </is>
       </c>
       <c r="D283" t="inlineStr">
@@ -13388,7 +13388,7 @@
       </c>
       <c r="C284" t="inlineStr">
         <is>
-          <t>Biobío</t>
+          <t>Biobio</t>
         </is>
       </c>
       <c r="D284" t="inlineStr">
@@ -13434,7 +13434,7 @@
       </c>
       <c r="C285" t="inlineStr">
         <is>
-          <t>Biobío</t>
+          <t>Biobio</t>
         </is>
       </c>
       <c r="D285" t="inlineStr">
@@ -13480,7 +13480,7 @@
       </c>
       <c r="C286" t="inlineStr">
         <is>
-          <t>La Araucanía</t>
+          <t>La Araucania</t>
         </is>
       </c>
       <c r="D286" t="inlineStr">
@@ -13526,7 +13526,7 @@
       </c>
       <c r="C287" t="inlineStr">
         <is>
-          <t>La Araucanía</t>
+          <t>La Araucania</t>
         </is>
       </c>
       <c r="D287" t="inlineStr">
@@ -13618,7 +13618,7 @@
       </c>
       <c r="C289" t="inlineStr">
         <is>
-          <t>La Araucanía</t>
+          <t>La Araucania</t>
         </is>
       </c>
       <c r="D289" t="inlineStr">
@@ -13664,7 +13664,7 @@
       </c>
       <c r="C290" t="inlineStr">
         <is>
-          <t>Biobío</t>
+          <t>Biobio</t>
         </is>
       </c>
       <c r="D290" t="inlineStr">
@@ -13710,7 +13710,7 @@
       </c>
       <c r="C291" t="inlineStr">
         <is>
-          <t>Biobío</t>
+          <t>Biobio</t>
         </is>
       </c>
       <c r="D291" t="inlineStr">
@@ -13756,7 +13756,7 @@
       </c>
       <c r="C292" t="inlineStr">
         <is>
-          <t>La Araucanía</t>
+          <t>La Araucania</t>
         </is>
       </c>
       <c r="D292" t="inlineStr">
@@ -13802,7 +13802,7 @@
       </c>
       <c r="C293" t="inlineStr">
         <is>
-          <t>Biobío</t>
+          <t>Biobio</t>
         </is>
       </c>
       <c r="D293" t="inlineStr">
@@ -13894,7 +13894,7 @@
       </c>
       <c r="C295" t="inlineStr">
         <is>
-          <t>Biobío</t>
+          <t>Biobio</t>
         </is>
       </c>
       <c r="D295" t="inlineStr">
@@ -14078,7 +14078,7 @@
       </c>
       <c r="C299" t="inlineStr">
         <is>
-          <t>La Araucanía</t>
+          <t>La Araucania</t>
         </is>
       </c>
       <c r="D299" t="inlineStr">
@@ -14124,7 +14124,7 @@
       </c>
       <c r="C300" t="inlineStr">
         <is>
-          <t>Biobío</t>
+          <t>Biobio</t>
         </is>
       </c>
       <c r="D300" t="inlineStr">
@@ -14216,7 +14216,7 @@
       </c>
       <c r="C302" t="inlineStr">
         <is>
-          <t>Biobío</t>
+          <t>Biobio</t>
         </is>
       </c>
       <c r="D302" t="inlineStr">
@@ -14308,7 +14308,7 @@
       </c>
       <c r="C304" t="inlineStr">
         <is>
-          <t>Biobío</t>
+          <t>Biobio</t>
         </is>
       </c>
       <c r="D304" t="inlineStr">
@@ -14354,7 +14354,7 @@
       </c>
       <c r="C305" t="inlineStr">
         <is>
-          <t>Biobío</t>
+          <t>Biobio</t>
         </is>
       </c>
       <c r="D305" t="inlineStr">
@@ -14400,7 +14400,7 @@
       </c>
       <c r="C306" t="inlineStr">
         <is>
-          <t>Biobío</t>
+          <t>Biobio</t>
         </is>
       </c>
       <c r="D306" t="inlineStr">
@@ -14446,7 +14446,7 @@
       </c>
       <c r="C307" t="inlineStr">
         <is>
-          <t>La Araucanía</t>
+          <t>La Araucania</t>
         </is>
       </c>
       <c r="D307" t="inlineStr">
@@ -14492,7 +14492,7 @@
       </c>
       <c r="C308" t="inlineStr">
         <is>
-          <t>Biobío</t>
+          <t>Biobio</t>
         </is>
       </c>
       <c r="D308" t="inlineStr">
@@ -14538,7 +14538,7 @@
       </c>
       <c r="C309" t="inlineStr">
         <is>
-          <t>Los Ríos</t>
+          <t>Los Rios</t>
         </is>
       </c>
       <c r="D309" t="inlineStr">
@@ -14584,7 +14584,7 @@
       </c>
       <c r="C310" t="inlineStr">
         <is>
-          <t>La Araucanía</t>
+          <t>La Araucania</t>
         </is>
       </c>
       <c r="D310" t="inlineStr">
@@ -14630,7 +14630,7 @@
       </c>
       <c r="C311" t="inlineStr">
         <is>
-          <t>La Araucanía</t>
+          <t>La Araucania</t>
         </is>
       </c>
       <c r="D311" t="inlineStr">
@@ -14676,7 +14676,7 @@
       </c>
       <c r="C312" t="inlineStr">
         <is>
-          <t>Biobío</t>
+          <t>Biobio</t>
         </is>
       </c>
       <c r="D312" t="inlineStr">
@@ -14722,7 +14722,7 @@
       </c>
       <c r="C313" t="inlineStr">
         <is>
-          <t>Los Ríos</t>
+          <t>Los Rios</t>
         </is>
       </c>
       <c r="D313" t="inlineStr">
@@ -14768,7 +14768,7 @@
       </c>
       <c r="C314" t="inlineStr">
         <is>
-          <t>Los Ríos</t>
+          <t>Los Rios</t>
         </is>
       </c>
       <c r="D314" t="inlineStr">
@@ -14814,7 +14814,7 @@
       </c>
       <c r="C315" t="inlineStr">
         <is>
-          <t>Los Ríos</t>
+          <t>Los Rios</t>
         </is>
       </c>
       <c r="D315" t="inlineStr">
@@ -14860,7 +14860,7 @@
       </c>
       <c r="C316" t="inlineStr">
         <is>
-          <t>Biobío</t>
+          <t>Biobio</t>
         </is>
       </c>
       <c r="D316" t="inlineStr">
@@ -14906,7 +14906,7 @@
       </c>
       <c r="C317" t="inlineStr">
         <is>
-          <t>La Araucanía</t>
+          <t>La Araucania</t>
         </is>
       </c>
       <c r="D317" t="inlineStr">
@@ -14952,7 +14952,7 @@
       </c>
       <c r="C318" t="inlineStr">
         <is>
-          <t>La Araucanía</t>
+          <t>La Araucania</t>
         </is>
       </c>
       <c r="D318" t="inlineStr">
@@ -15044,7 +15044,7 @@
       </c>
       <c r="C320" t="inlineStr">
         <is>
-          <t>Biobío</t>
+          <t>Biobio</t>
         </is>
       </c>
       <c r="D320" t="inlineStr">
@@ -15090,7 +15090,7 @@
       </c>
       <c r="C321" t="inlineStr">
         <is>
-          <t>Biobío</t>
+          <t>Biobio</t>
         </is>
       </c>
       <c r="D321" t="inlineStr">
@@ -15136,7 +15136,7 @@
       </c>
       <c r="C322" t="inlineStr">
         <is>
-          <t>Biobío</t>
+          <t>Biobio</t>
         </is>
       </c>
       <c r="D322" t="inlineStr">
@@ -15182,7 +15182,7 @@
       </c>
       <c r="C323" t="inlineStr">
         <is>
-          <t>Los Ríos</t>
+          <t>Los Rios</t>
         </is>
       </c>
       <c r="D323" t="inlineStr">
@@ -15228,7 +15228,7 @@
       </c>
       <c r="C324" t="inlineStr">
         <is>
-          <t>Biobío</t>
+          <t>Biobio</t>
         </is>
       </c>
       <c r="D324" t="inlineStr">
@@ -15274,7 +15274,7 @@
       </c>
       <c r="C325" t="inlineStr">
         <is>
-          <t>La Araucanía</t>
+          <t>La Araucania</t>
         </is>
       </c>
       <c r="D325" t="inlineStr">
@@ -15366,7 +15366,7 @@
       </c>
       <c r="C327" t="inlineStr">
         <is>
-          <t>La Araucanía</t>
+          <t>La Araucania</t>
         </is>
       </c>
       <c r="D327" t="inlineStr">
@@ -15412,7 +15412,7 @@
       </c>
       <c r="C328" t="inlineStr">
         <is>
-          <t>Biobío</t>
+          <t>Biobio</t>
         </is>
       </c>
       <c r="D328" t="inlineStr">
@@ -15458,7 +15458,7 @@
       </c>
       <c r="C329" t="inlineStr">
         <is>
-          <t>Los Ríos</t>
+          <t>Los Rios</t>
         </is>
       </c>
       <c r="D329" t="inlineStr">

--- a/output/graficos_nacionales/plot_nacional_e_rezjov_a_2021.xlsx
+++ b/output/graficos_nacionales/plot_nacional_e_rezjov_a_2021.xlsx
@@ -2086,7 +2086,7 @@
     <t xml:space="preserve">Fecha de creación</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-07-30 15:40</t>
+    <t xml:space="preserve">2026-09-07 12:57</t>
   </si>
   <si>
     <t xml:space="preserve">Fuente</t>

--- a/output/graficos_nacionales/plot_nacional_e_rezjov_a_2021.xlsx
+++ b/output/graficos_nacionales/plot_nacional_e_rezjov_a_2021.xlsx
@@ -2086,7 +2086,7 @@
     <t xml:space="preserve">Fecha de creación</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-09-07 12:57</t>
+    <t xml:space="preserve">2026-09-08 10:28</t>
   </si>
   <si>
     <t xml:space="preserve">Fuente</t>
